--- a/タスク管理エージェント/ビジネスキャンプ/ビジネスキャンプ_収支と決めること.xlsx
+++ b/タスク管理エージェント/ビジネスキャンプ/ビジネスキャンプ_収支と決めること.xlsx
@@ -152,81 +152,294 @@
     <t xml:space="preserve">宿泊＋3食 子ども（1人）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">宿泊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円＋宿泊税</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円＋朝食</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円＋昼食</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円＋鍋</t>
+    <t xml:space="preserve">宿泊1,100円＋宿泊税200円＋朝食800円＋昼食1,000円＋鍋3,000円（Kazuさん確認）。以前の8,800円から変更</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宿泊＋3食 スタッフ（1人）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宿泊3,400円（税込）＋朝食800円＋昼食1,000円＋鍋3,500円</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スタッフ日給（1日目）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Kazu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">さん</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">スタッフ日給（2日目）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Kazu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">さん。半日近いため</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">会場（研修室2日分）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Kazu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">さん：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円。公式料金は要確認</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">運営への支払い</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Kazu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">さん。会場等とは別</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">おやつ・飲み物</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仮定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">iPad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">レンタル（台数）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">台</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">iPad 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台あたり</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">仮定：個人向けは2日で約2,000円前後。法人は要見積もり</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">iPad </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配送料</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gemini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">有料アカウント</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月無料体験を使う想定。無料期間後や条件は要確認（有料なら約</t>
     </r>
     <r>
       <rPr>
@@ -243,114 +456,791 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kazu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">さん確認）。以前の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8,800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円から変更</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">宿泊＋3食 スタッフ（1人）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宿泊3,400円（税込）＋朝食800円＋昼食1,000円＋鍋3,500円</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スタッフ日給（1日目）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kazu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">さん</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">スタッフ日給（2日目）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kazu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">さん。半日近いため</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">会場（研修室2日分）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kazu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">さん：</t>
-    </r>
+      <t xml:space="preserve">円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台数）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗品（印刷・飴・賞状・コイン）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">イベント保険</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仮定。要見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手取りの目標</t>
+  </si>
+  <si>
+    <t xml:space="preserve">収入と費用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加費収入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宿泊＋3食（子ども）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宿泊＋3食（スタッフ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スタッフ日給</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会場</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">iPad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（レンタル＋配送）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gemini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アカウント</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗品</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保険</t>
+  </si>
+  <si>
+    <t xml:space="preserve">費用合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">利益（手取り）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人あたり利益</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">損益分岐点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">子ども1人あたりの変動費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">固定費（人数に関係しない費用）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">損益分岐の人数（人）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手取り目標を達成する人数（人）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加人数別の利益（円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加人数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">収入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">費用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">利益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内容</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:20</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">開会、Dreamコイン100万円を配る</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:40</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ペア決め（AIは2人1台）、1人ずつ自己紹介</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:55</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">かけっこ（学年グループ別）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:55</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">行き先を選ぶ（交通費を払う）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の使い方レッスン</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:40</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">クエスト1：地域調べ（3行メモ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:55</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">宿を選ぶ、椅子取りゲーム、ご当地クイズ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:55</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:15</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">クエスト2：タイトルとキャッチコピー、投票</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:30</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">おやつ、休憩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">クエスト3：スケジュール作り</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:20</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">サイコロ1回目</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ミニ発表、お客さんコイン50万円で買う、団体客ルーレット1回目</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:30</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">サイコロ2回目、振り返り</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:30</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夕食（鍋）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19:30</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">入浴</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ゲーム（任意）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21:30</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">自由時間</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">就寝準備、消灯</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -366,6 +1256,25 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">日目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">〜</t>
     </r>
     <r>
@@ -375,44 +1284,365 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円。公式料金は要確認</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">運営への支払い</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kazu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">さん。会場等とは別</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">おやつ・飲み物</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仮定</t>
+      <t xml:space="preserve">9:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">起床、朝食、準備</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9:15</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">開始、サイコロ3回目</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9:15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10:45</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">クエスト4・5：広報ポスターと動画（Gemini10秒）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10:45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">作品を貼り出して投票</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11:10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">団体客ルーレット2回</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11:10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">本番ピッチ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12:15</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">お客さんコイン50万円で買う</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12:15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">精算、表彰</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">昼食、解散準備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">分類</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状況</t>
+  </si>
+  <si>
+    <t xml:space="preserve">担当・確認先</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">運営への15万円の中身（会場・宿泊を含まない別費用で確定）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">決定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">子どもの宿泊＋3食＝約6,100円（宿泊1,100＋宿泊税200＋朝800＋昼1,000＋鍋3,000）、スタッフ＝約8,700円。施設に最終確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">施設に確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加費：4万円を基本に</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スタッフ人数（2人か3人）と日給（1日目1.5万、2日目1万）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会場料金（2日で2〜3万円）の正式な見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あうる京北の正式な料金表、空室、Wi-Fi、入浴・消灯のルール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電話：075-854-0216（検索結果の記載）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夕食を鍋にする場合の追加料金や持ち込みの可否</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">動画：スタッフの有料Geminiアカウントを子どもが使う（確定）。1か月無料体験で始める</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">歳未満の子どもが操作して問題ないか、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式の条件を確認</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">無料体験の期間・解約手順（体験後に請求が発生しないようにする）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ChatGPT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無料版の画像生成の回数。前日に実機で確認</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">保護者のAI利用同意は、申込時にまとめて取る（確定）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">端末</t>
   </si>
   <si>
     <r>
@@ -430,13 +1660,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">レンタル（台数）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">台</t>
-  </si>
-  <si>
+      <t xml:space="preserve">の台数（</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -452,1357 +1677,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">iPad 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台あたり</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">仮定：個人向けは2日で約2,000円前後。法人は要見積もり</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">iPad </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配送料</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Gemini</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">有料アカウント</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月無料体験を使う想定。無料期間後や条件は要確認（有料なら約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台数）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">消耗品（印刷・飴・賞状・コイン）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">イベント保険</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仮定。要見積もり</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手取りの目標</t>
-  </si>
-  <si>
-    <t xml:space="preserve">収入と費用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参加費収入</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宿泊＋3食（子ども）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宿泊＋3食（スタッフ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スタッフ日給</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会場</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">iPad</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（レンタル＋配送）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Gemini</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">アカウント</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">消耗品</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保険</t>
-  </si>
-  <si>
-    <t xml:space="preserve">費用合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">利益（手取り）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人あたり利益</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">損益分岐点</t>
-  </si>
-  <si>
-    <t xml:space="preserve">子ども1人あたりの変動費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">固定費（人数に関係しない費用）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">損益分岐の人数（人）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手取り目標を達成する人数（人）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参加人数別の利益（円）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参加人数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">収入</t>
-  </si>
-  <si>
-    <t xml:space="preserve">費用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">利益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日</t>
-  </si>
-  <si>
-    <t xml:space="preserve">時間</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内容</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:20</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">開会、Dreamコイン100万円を配る</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:40</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ペア決め（AIは2人1台）、1人ずつ自己紹介</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:55</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">かけっこ（学年グループ別）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:55</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:10</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">行き先を選ぶ（交通費を払う）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:20</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の使い方レッスン</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:40</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">クエスト1：地域調べ（3行メモ）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:55</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">宿を選ぶ、椅子取りゲーム、ご当地クイズ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:55</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15:15</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">クエスト2：タイトルとキャッチコピー、投票</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15:15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15:30</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">おやつ、休憩</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">クエスト3：スケジュール作り</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16:20</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">サイコロ1回目</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16:20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ミニ発表、お客さんコイン50万円で買う、団体客ルーレット1回目</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17:30</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">サイコロ2回目、振り返り</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18:30</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">夕食（鍋）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19:30</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">入浴</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20:30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ゲーム（任意）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21:30</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">自由時間</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">就寝準備、消灯</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">起床、朝食、準備</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9:15</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">開始、サイコロ3回目</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9:15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10:45</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">クエスト4・5：広報ポスターと動画（Gemini10秒）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10:45</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">作品を貼り出して投票</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11:10</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">団体客ルーレット2回</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11:10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">本番ピッチ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12:15</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">お客さんコイン50万円で買う</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12:15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">精算、表彰</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">昼食、解散準備</t>
-  </si>
-  <si>
-    <t xml:space="preserve">分類</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状況</t>
-  </si>
-  <si>
-    <t xml:space="preserve">担当・確認先</t>
-  </si>
-  <si>
-    <t xml:space="preserve">お金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">運営への15万円の中身（会場・宿泊を含まない別費用で確定）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">決定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">子どもの宿泊＋3食＝約6,100円（宿泊1,100＋宿泊税200＋朝800＋昼1,000＋鍋3,000）、スタッフ＝約8,700円。施設に最終確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">施設に確認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参加費：4万円を基本に</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スタッフ人数（2人か3人）と日給（1日目1.5万、2日目1万）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会場料金（2日で2〜3万円）の正式な見積もり</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あうる京北の正式な料金表、空室、Wi-Fi、入浴・消灯のルール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">電話：075-854-0216（検索結果の記載）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">夕食を鍋にする場合の追加料金や持ち込みの可否</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">動画：スタッフの有料Geminiアカウントを子どもが使う（確定）。1か月無料体験で始める</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">歳未満の子どもが操作して問題ないか、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Google</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式の条件を確認</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">無料体験の期間・解約手順（体験後に請求が発生しないようにする）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ChatGPT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無料版の画像生成の回数。前日に実機で確認</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">保護者のAI利用同意は、申込時にまとめて取る（確定）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">端末</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">iPad</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の台数（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">人なら</t>
     </r>
     <r>
@@ -1830,7 +1704,7 @@
     <t xml:space="preserve">ルール</t>
   </si>
   <si>
-    <t xml:space="preserve">サイコロ「4」の判定はKazuさんが行う（確定）</t>
+    <t xml:space="preserve">サイコロ「4」はAI審査員（意外性・行き先らしさ・伝わりやすさ各3点、6点以上で成功）。最終判断はKazuさん</t>
   </si>
   <si>
     <t xml:space="preserve">ご当地クイズの問題作成（当日、選ばれた県から）</t>
@@ -2004,7 +1878,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2034,10 +1908,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2418,7 +2288,7 @@
       <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2468,7 +2338,7 @@
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="8" t="n">
         <v>30000</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -2496,7 +2366,7 @@
       <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="8" t="n">
         <v>10000</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -2524,7 +2394,7 @@
       <c r="A16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="8" t="n">
         <v>3000</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2538,7 +2408,7 @@
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="8" t="n">
         <v>3000</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -2552,7 +2422,7 @@
       <c r="A18" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -2566,7 +2436,7 @@
       <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="8" t="n">
         <v>15000</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -2580,7 +2450,7 @@
       <c r="A20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="8" t="n">
         <v>15000</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -2611,7 +2481,7 @@
       <c r="D22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B23" s="3"/>
@@ -2622,7 +2492,7 @@
       <c r="A24" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="10" t="n">
         <f aca="false">$B$5*$B$6</f>
         <v>600000</v>
       </c>
@@ -2633,7 +2503,7 @@
       <c r="A25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="10" t="n">
         <f aca="false">$B$5*$B$8</f>
         <v>91500</v>
       </c>
@@ -2644,7 +2514,7 @@
       <c r="A26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="10" t="n">
         <f aca="false">$B$7*$B$9</f>
         <v>17400</v>
       </c>
@@ -2655,7 +2525,7 @@
       <c r="A27" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="10" t="n">
         <f aca="false">$B$7*($B$10+$B$11)</f>
         <v>50000</v>
       </c>
@@ -2666,7 +2536,7 @@
       <c r="A28" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="10" t="n">
         <f aca="false">$B$12</f>
         <v>30000</v>
       </c>
@@ -2677,7 +2547,7 @@
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="10" t="n">
         <f aca="false">$B$13</f>
         <v>150000</v>
       </c>
@@ -2688,7 +2558,7 @@
       <c r="A30" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="10" t="n">
         <f aca="false">$B$14</f>
         <v>10000</v>
       </c>
@@ -2699,7 +2569,7 @@
       <c r="A31" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="10" t="n">
         <f aca="false">$B$15*$B$16+$B$17</f>
         <v>27000</v>
       </c>
@@ -2710,7 +2580,7 @@
       <c r="A32" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="10" t="n">
         <f aca="false">$B$18</f>
         <v>0</v>
       </c>
@@ -2721,7 +2591,7 @@
       <c r="A33" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B33" s="10" t="n">
         <f aca="false">$B$19</f>
         <v>15000</v>
       </c>
@@ -2732,7 +2602,7 @@
       <c r="A34" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="10" t="n">
         <f aca="false">$B$20</f>
         <v>15000</v>
       </c>
@@ -2740,10 +2610,10 @@
       <c r="D34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="11" t="n">
         <f aca="false">SUM(B25:B34)</f>
         <v>405900</v>
       </c>
@@ -2751,10 +2621,10 @@
       <c r="D35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="11" t="n">
         <f aca="false">B24-B35</f>
         <v>194100</v>
       </c>
@@ -2765,7 +2635,7 @@
       <c r="A37" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="11" t="n">
+      <c r="B37" s="10" t="n">
         <f aca="false">B36/$B$5</f>
         <v>12940</v>
       </c>
@@ -2779,7 +2649,7 @@
       <c r="D38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="3"/>
@@ -2790,7 +2660,7 @@
       <c r="A40" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B40" s="10" t="n">
         <f aca="false">$B$8</f>
         <v>6100</v>
       </c>
@@ -2801,7 +2671,7 @@
       <c r="A41" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="11" t="n">
+      <c r="B41" s="10" t="n">
         <f aca="false">B35-$B$5*$B$8</f>
         <v>314400</v>
       </c>
@@ -2812,7 +2682,7 @@
       <c r="A42" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="13" t="n">
+      <c r="B42" s="12" t="n">
         <f aca="false">ROUNDUP(B41/($B$6-B40),0)</f>
         <v>10</v>
       </c>
@@ -2823,7 +2693,7 @@
       <c r="A43" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="12" t="n">
         <f aca="false">ROUNDUP((B41+$B$21)/($B$6-B40),0)</f>
         <v>13</v>
       </c>
@@ -2837,7 +2707,7 @@
       <c r="D44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="9" t="s">
         <v>58</v>
       </c>
       <c r="B45" s="3"/>
@@ -2859,154 +2729,154 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="14" t="n">
+      <c r="A47" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B47" s="11" t="n">
+      <c r="B47" s="10" t="n">
         <f aca="false">A47*$B$6</f>
         <v>400000</v>
       </c>
-      <c r="C47" s="11" t="n">
+      <c r="C47" s="10" t="n">
         <f aca="false">B41+A47*$B$8</f>
         <v>375400</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="10" t="n">
         <f aca="false">B47-C47</f>
         <v>24600</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="14" t="n">
+      <c r="A48" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B48" s="11" t="n">
+      <c r="B48" s="10" t="n">
         <f aca="false">A48*$B$6</f>
         <v>440000</v>
       </c>
-      <c r="C48" s="11" t="n">
+      <c r="C48" s="10" t="n">
         <f aca="false">B41+A48*$B$8</f>
         <v>381500</v>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="10" t="n">
         <f aca="false">B48-C48</f>
         <v>58500</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="14" t="n">
+      <c r="A49" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="11" t="n">
+      <c r="B49" s="10" t="n">
         <f aca="false">A49*$B$6</f>
         <v>480000</v>
       </c>
-      <c r="C49" s="11" t="n">
+      <c r="C49" s="10" t="n">
         <f aca="false">B41+A49*$B$8</f>
         <v>387600</v>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="10" t="n">
         <f aca="false">B49-C49</f>
         <v>92400</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14" t="n">
+      <c r="A50" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B50" s="11" t="n">
+      <c r="B50" s="10" t="n">
         <f aca="false">A50*$B$6</f>
         <v>520000</v>
       </c>
-      <c r="C50" s="11" t="n">
+      <c r="C50" s="10" t="n">
         <f aca="false">B41+A50*$B$8</f>
         <v>393700</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="10" t="n">
         <f aca="false">B50-C50</f>
         <v>126300</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="14" t="n">
+      <c r="A51" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B51" s="11" t="n">
+      <c r="B51" s="10" t="n">
         <f aca="false">A51*$B$6</f>
         <v>560000</v>
       </c>
-      <c r="C51" s="11" t="n">
+      <c r="C51" s="10" t="n">
         <f aca="false">B41+A51*$B$8</f>
         <v>399800</v>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="10" t="n">
         <f aca="false">B51-C51</f>
         <v>160200</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="14" t="n">
+      <c r="A52" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B52" s="11" t="n">
+      <c r="B52" s="10" t="n">
         <f aca="false">A52*$B$6</f>
         <v>600000</v>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C52" s="10" t="n">
         <f aca="false">B41+A52*$B$8</f>
         <v>405900</v>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D52" s="10" t="n">
         <f aca="false">B52-C52</f>
         <v>194100</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="14" t="n">
+      <c r="A53" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B53" s="11" t="n">
+      <c r="B53" s="10" t="n">
         <f aca="false">A53*$B$6</f>
         <v>640000</v>
       </c>
-      <c r="C53" s="11" t="n">
+      <c r="C53" s="10" t="n">
         <f aca="false">B41+A53*$B$8</f>
         <v>412000</v>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D53" s="10" t="n">
         <f aca="false">B53-C53</f>
         <v>228000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="14" t="n">
+      <c r="A54" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B54" s="11" t="n">
+      <c r="B54" s="10" t="n">
         <f aca="false">A54*$B$6</f>
         <v>680000</v>
       </c>
-      <c r="C54" s="11" t="n">
+      <c r="C54" s="10" t="n">
         <f aca="false">B41+A54*$B$8</f>
         <v>418100</v>
       </c>
-      <c r="D54" s="11" t="n">
+      <c r="D54" s="10" t="n">
         <f aca="false">B54-C54</f>
         <v>261900</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="14" t="n">
+      <c r="A55" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B55" s="11" t="n">
+      <c r="B55" s="10" t="n">
         <f aca="false">A55*$B$6</f>
         <v>720000</v>
       </c>
-      <c r="C55" s="11" t="n">
+      <c r="C55" s="10" t="n">
         <f aca="false">B41+A55*$B$8</f>
         <v>424200</v>
       </c>
-      <c r="D55" s="11" t="n">
+      <c r="D55" s="10" t="n">
         <f aca="false">B55-C55</f>
         <v>295800</v>
       </c>
@@ -3431,7 +3301,7 @@
       <c r="B5" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -3445,7 +3315,7 @@
       <c r="B6" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -3459,7 +3329,7 @@
       <c r="B7" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -3473,7 +3343,7 @@
       <c r="B8" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -3501,7 +3371,7 @@
       <c r="B10" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -3515,7 +3385,7 @@
       <c r="B11" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D11" s="7" t="s">
@@ -3529,7 +3399,7 @@
       <c r="B12" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D12" s="7" t="s">
@@ -3557,7 +3427,7 @@
       <c r="B14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -3571,7 +3441,7 @@
       <c r="B15" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -3599,7 +3469,7 @@
       <c r="B17" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D17" s="7" t="s">
@@ -3613,7 +3483,7 @@
       <c r="B18" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D18" s="7" t="s">
@@ -3627,7 +3497,7 @@
       <c r="B19" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>132</v>
       </c>
       <c r="D19" s="7" t="s">

--- a/タスク管理エージェント/ビジネスキャンプ/ビジネスキャンプ_収支と決めること.xlsx
+++ b/タスク管理エージェント/ビジネスキャンプ/ビジネスキャンプ_収支と決めること.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="156">
   <si>
     <t xml:space="preserve">ビジネスキャンプ「AI旅行会社」 収支シミュレーション</t>
   </si>
@@ -652,7 +652,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万円を配る、ルール説明</t>
+      <t xml:space="preserve">万円、ルール説明</t>
     </r>
   </si>
   <si>
@@ -765,7 +765,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">行き先を選ぶ（都道府県カード、じゃんけん順、同じ県なし）。交通費を払う</t>
+    <t xml:space="preserve">行き先を選ぶ（カード、じゃんけん順、同じ県なし）。交通費</t>
   </si>
   <si>
     <r>
@@ -811,8 +811,100 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">サイクル① 行き先だけを</t>
-    </r>
+      <t xml:space="preserve">サイクル① 行き先</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:50</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">地域調べ（ご当地クイズを統合）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">宿を選ぶ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:15</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -828,18 +920,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">に入れる（チュートリアル）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:20</t>
+      <t xml:space="preserve">サイクル② 行き先＋宿</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:15</t>
     </r>
     <r>
       <rPr>
@@ -856,21 +948,21 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">14:50</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">地域調べ（ご当地クイズを統合）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:50</t>
+      <t xml:space="preserve">15:30</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">おやつ、休憩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:30</t>
     </r>
     <r>
       <rPr>
@@ -887,21 +979,21 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15:05</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">宿を選ぶ（宿代を払う）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15:05</t>
+      <t xml:space="preserve">16:05</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">タイトル・キャッチコピー・ポスター画像</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:05</t>
     </r>
     <r>
       <rPr>
@@ -918,7 +1010,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15:25</t>
+      <t xml:space="preserve">16:20</t>
     </r>
   </si>
   <si>
@@ -937,18 +1029,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">サイクル② 行き先＋宿</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15:25</t>
+      <t xml:space="preserve">サイクル③ タイトル・コピー・画像</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:20</t>
     </r>
     <r>
       <rPr>
@@ -965,21 +1057,45 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15:40</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">おやつ、休憩</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15:40</t>
+      <t xml:space="preserve">16:40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">旅行スケジュール（行き先・宿・観光スポット</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か所）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:40</t>
     </r>
     <r>
       <rPr>
@@ -996,21 +1112,37 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">16:20</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">タイトル・キャッチコピー、広報ポスター（広告は自由）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16:20</t>
+      <t xml:space="preserve">16:55</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">サイクル④ 旅行スケジュール</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:55</t>
     </r>
     <r>
       <rPr>
@@ -1027,10 +1159,90 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">16:40</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">17:05</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告を作る（任意。広告費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:35</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ミニ発表（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒）、</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1046,18 +1258,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">サイクル③ コピー・ポスター・広告</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16:40</t>
+      <t xml:space="preserve">サイクル⑤ 全部を入れる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:35</t>
     </r>
     <r>
       <rPr>
@@ -1074,7 +1286,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">17:00</t>
+      <t xml:space="preserve">18:00</t>
     </r>
   </si>
   <si>
@@ -1101,6 +1313,23 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">回目、団体客ルーレット</t>
     </r>
     <r>
@@ -1118,6 +1347,259 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">回目、振り返り</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夕食（鍋）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">入浴</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21:30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スマイルゲーム、自由時間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ゲームは任意）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">就寝準備、消灯</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">起床、朝食、準備</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9:15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">開始、サイコロ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">回目</t>
     </r>
   </si>
@@ -1129,7 +1611,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">17:00</t>
+      <t xml:space="preserve">9:15</t>
     </r>
     <r>
       <rPr>
@@ -1146,17 +1628,34 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">17:30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">サイコロ</t>
+      <t xml:space="preserve">10:45</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">考える時間（全部やり直し、最後に動画）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頃に団体客ルーレット</t>
     </r>
     <r>
       <rPr>
@@ -1173,18 +1672,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回目、振り返り</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17:30</t>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10:45</t>
     </r>
     <r>
       <rPr>
@@ -1201,21 +1700,45 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">18:30</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">夕食（鍋）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18:30</t>
+      <t xml:space="preserve">10:55</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">団体客ルーレット</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目、最終ピッチの準備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10:55</t>
     </r>
     <r>
       <rPr>
@@ -1232,21 +1755,45 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">19:30</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">入浴</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19:30</t>
+      <t xml:space="preserve">11:50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">最終ピッチ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">サイクル⑥</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11:50</t>
     </r>
     <r>
       <rPr>
@@ -1263,45 +1810,54 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">21:30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スマイルゲーム、自由時間（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ゲームは任意）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21:30</t>
+      <t xml:space="preserve">12:05</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ペルソナが購入判定。お客さんコイン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円を発動</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12:05</t>
     </r>
     <r>
       <rPr>
@@ -1318,13 +1874,307 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">22:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">就寝準備、消灯</t>
-  </si>
-  <si>
+      <t xml:space="preserve">12:15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">団体客ルーレット</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目、親への</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投票</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12:15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:00</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">精算、表彰</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">昼食（未定）、解散準備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">分類</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状況</t>
+  </si>
+  <si>
+    <t xml:space="preserve">担当・確認先</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最優先</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ペルソナ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の作成と精度確認（年齢・家族構成・値段感・好み・広告効果の重み）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">未定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">かず（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月中旬）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">審査アプリ、サイコロ・ルーレットアプリの作成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">かず</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ルール</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">賞金の人数・金額（案：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">評価の上位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">動画の作り方（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gemini</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のアカウント、子どもが作る場合の条件）と、運営のまとめ動画を続けるか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">広告は自由、出す場合の広告費</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円、出した人はルーレット</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1340,148 +2190,80 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">口</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">決定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">サイクルは計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">日目</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">起床、朝食、準備</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9:15</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">開始、サイコロ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9:15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10:45</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">考える時間（広告・コピー・ポスターなどを全部やり直す）。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">頃に団体客ルーレット</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回、</t>
     </r>
     <r>
       <rPr>
@@ -1498,100 +2280,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10:45</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10:55</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">団体客ルーレット</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目、最終ピッチの準備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10:55</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11:50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最終ピッチ（</t>
+      <t xml:space="preserve">日目</t>
     </r>
     <r>
       <rPr>
@@ -1608,7 +2297,96 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">人</t>
+      <t xml:space="preserve">回）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行き先はカード＋じゃんけん順、同じ県なし／子ども同士の投票なし／団体客ルーレットは計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">値段の上限は残す。お客さんコインは最終ピッチで発動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">場所・移動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">集合時間・場所、バス・宿の時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiroko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">遠方参加者の移動サポート、昼食の扱い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お金</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参加費：関西</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">38,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円／関東</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円。保険は不要。スタッフは</t>
     </r>
     <r>
       <rPr>
@@ -1625,563 +2403,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分、値段を発表）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11:50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12:05</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ペルソナが購入判定。お客さんコイン</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円で他の人のツアーを購入</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12:05</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12:15</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">団体客ルーレット</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目、親への</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LINE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投票</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12:15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:00</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">精算、表彰</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">昼食（未定）、解散準備</t>
-  </si>
-  <si>
-    <t xml:space="preserve">分類</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状況</t>
-  </si>
-  <si>
-    <t xml:space="preserve">担当・確認先</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最優先</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ペルソナ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名の作成と精度確認（年齢・家族構成・値段感・好み・広告効果の重み）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">未定</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">かず（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月中旬）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">審査アプリ、サイコロ・ルーレットアプリの作成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">かず</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ルール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">広告費の金額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">かず・山田</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">サイクルの回数（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回か</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日目の考える時間に動画づくりを入れるか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">評価で賞金を出すか、広告を出した人の団体客ルーレットの枠を増やすか</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">行き先はカード＋じゃんけん順、同じ県なし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">決定</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">子ども同士の投票はなし。団体客ルーレットは残す（計</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">値段の上限は残す。お客さんコインは最終ピッチのみ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">場所・移動</t>
-  </si>
-  <si>
-    <t xml:space="preserve">集合時間・場所、バス・宿の時間</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiroko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">遠方参加者の移動サポート、昼食の扱い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">お金</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">参加費：関西</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">38,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円／関東</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">42,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円。保険は不要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">会議・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kazu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">さん</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スタッフ人数（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名か</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名）、会場の正式料金、</t>
+      <t xml:space="preserve">名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">会場の正式料金、</t>
     </r>
     <r>
       <rPr>
@@ -3534,12 +3766,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3681,11 +3913,11 @@
       <c r="B13" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
         <v>66</v>
       </c>
@@ -3696,7 +3928,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
         <v>66</v>
       </c>
@@ -3731,40 +3963,40 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="B19" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="16" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B20" s="15" t="s">
+      <c r="C20" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="16" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>99</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>106</v>
@@ -3775,7 +4007,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>108</v>
@@ -3786,18 +4018,18 @@
     </row>
     <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="16" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>112</v>
@@ -3806,9 +4038,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>114</v>
@@ -3817,15 +4049,48 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="15" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3844,7 +4109,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -3855,83 +4120,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>65</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="16" t="s">
         <v>129</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="16" t="s">
         <v>129</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>123</v>
+        <v>133</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>137</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>19</v>
@@ -3939,13 +4204,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>123</v>
+        <v>138</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>137</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>19</v>
@@ -3953,13 +4218,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>19</v>
@@ -3967,13 +4232,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>19</v>
@@ -3981,114 +4246,100 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>134</v>
+        <v>142</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>129</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>19</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>123</v>
-      </c>
       <c r="D12" s="15" t="s">
-        <v>139</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>143</v>
+        <v>147</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>19</v>
+        <v>129</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>123</v>
+        <v>152</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>137</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>155</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
